--- a/data/manual/toto節リスト.xlsx
+++ b/data/manual/toto節リスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dev_tomo/Desktop/tt_prj_restart/data/manual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A7DC6F-DB59-2E43-97FD-D00A1C9AD9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{499FC87F-D553-DC4F-88F4-7AD33E22526B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1620" yWindow="1360" windowWidth="27200" windowHeight="16940" xr2:uid="{523FC2FC-BED5-B640-BD42-B6B48CE3A411}"/>
+    <workbookView xWindow="7340" yWindow="2240" windowWidth="27200" windowHeight="16940" xr2:uid="{523FC2FC-BED5-B640-BD42-B6B48CE3A411}"/>
   </bookViews>
   <sheets>
     <sheet name="toto節リスト" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="97">
   <si>
     <t>totoオフィシャルサイトのtoto購入画面（html表面）から試合組み合わせテーブルのテキストをコピー</t>
     <rPh sb="18" eb="22">
@@ -465,7 +465,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -508,8 +508,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -545,6 +557,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -554,7 +575,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -603,13 +624,46 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -950,7 +1004,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:J235"/>
+  <dimension ref="A1:J352"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -4902,7 +4956,7 @@
       <c r="A171" s="10">
         <v>2026</v>
       </c>
-      <c r="B171" s="16">
+      <c r="B171">
         <v>1626</v>
       </c>
       <c r="C171" s="10">
@@ -4926,7 +4980,7 @@
       <c r="A172" s="10">
         <v>2026</v>
       </c>
-      <c r="B172" s="16">
+      <c r="B172">
         <v>1626</v>
       </c>
       <c r="C172" s="10">
@@ -4950,7 +5004,7 @@
       <c r="A173" s="10">
         <v>2026</v>
       </c>
-      <c r="B173" s="16">
+      <c r="B173">
         <v>1626</v>
       </c>
       <c r="C173" s="10">
@@ -4974,7 +5028,7 @@
       <c r="A174" s="10">
         <v>2026</v>
       </c>
-      <c r="B174" s="16">
+      <c r="B174">
         <v>1626</v>
       </c>
       <c r="C174" s="10">
@@ -4998,7 +5052,7 @@
       <c r="A175" s="10">
         <v>2026</v>
       </c>
-      <c r="B175" s="16">
+      <c r="B175">
         <v>1626</v>
       </c>
       <c r="C175" s="10">
@@ -5022,7 +5076,7 @@
       <c r="A176" s="10">
         <v>2026</v>
       </c>
-      <c r="B176" s="16">
+      <c r="B176">
         <v>1626</v>
       </c>
       <c r="C176" s="10">
@@ -5046,7 +5100,7 @@
       <c r="A177" s="10">
         <v>2026</v>
       </c>
-      <c r="B177" s="16">
+      <c r="B177">
         <v>1626</v>
       </c>
       <c r="C177" s="10">
@@ -5070,7 +5124,7 @@
       <c r="A178" s="10">
         <v>2026</v>
       </c>
-      <c r="B178" s="16">
+      <c r="B178">
         <v>1626</v>
       </c>
       <c r="C178" s="10">
@@ -5094,7 +5148,7 @@
       <c r="A179" s="10">
         <v>2026</v>
       </c>
-      <c r="B179" s="16">
+      <c r="B179">
         <v>1626</v>
       </c>
       <c r="C179" s="10">
@@ -5118,7 +5172,7 @@
       <c r="A180" s="10">
         <v>2026</v>
       </c>
-      <c r="B180" s="16">
+      <c r="B180">
         <v>1626</v>
       </c>
       <c r="C180" s="10">
@@ -5142,7 +5196,7 @@
       <c r="A181" s="10">
         <v>2026</v>
       </c>
-      <c r="B181" s="16">
+      <c r="B181">
         <v>1626</v>
       </c>
       <c r="C181" s="10">
@@ -5166,7 +5220,7 @@
       <c r="A182" s="10">
         <v>2026</v>
       </c>
-      <c r="B182" s="16">
+      <c r="B182">
         <v>1626</v>
       </c>
       <c r="C182" s="10">
@@ -5190,7 +5244,7 @@
       <c r="A183" s="10">
         <v>2026</v>
       </c>
-      <c r="B183" s="16">
+      <c r="B183">
         <v>1626</v>
       </c>
       <c r="C183" s="10">
@@ -5214,10 +5268,10 @@
       <c r="A184" s="10">
         <v>2026</v>
       </c>
-      <c r="B184" s="17">
+      <c r="B184" s="16">
         <v>1627</v>
       </c>
-      <c r="C184" s="17">
+      <c r="C184" s="16">
         <v>15</v>
       </c>
       <c r="D184">
@@ -5238,10 +5292,10 @@
       <c r="A185" s="10">
         <v>2026</v>
       </c>
-      <c r="B185" s="17">
+      <c r="B185" s="16">
         <v>1627</v>
       </c>
-      <c r="C185" s="17">
+      <c r="C185" s="16">
         <v>15</v>
       </c>
       <c r="D185">
@@ -5262,10 +5316,10 @@
       <c r="A186" s="10">
         <v>2026</v>
       </c>
-      <c r="B186" s="17">
+      <c r="B186" s="16">
         <v>1627</v>
       </c>
-      <c r="C186" s="17">
+      <c r="C186" s="16">
         <v>15</v>
       </c>
       <c r="D186">
@@ -5286,10 +5340,10 @@
       <c r="A187" s="10">
         <v>2026</v>
       </c>
-      <c r="B187" s="17">
+      <c r="B187" s="16">
         <v>1627</v>
       </c>
-      <c r="C187" s="17">
+      <c r="C187" s="16">
         <v>15</v>
       </c>
       <c r="D187">
@@ -5310,10 +5364,10 @@
       <c r="A188" s="10">
         <v>2026</v>
       </c>
-      <c r="B188" s="17">
+      <c r="B188" s="16">
         <v>1627</v>
       </c>
-      <c r="C188" s="17">
+      <c r="C188" s="16">
         <v>15</v>
       </c>
       <c r="D188">
@@ -5334,10 +5388,10 @@
       <c r="A189" s="10">
         <v>2026</v>
       </c>
-      <c r="B189" s="17">
+      <c r="B189" s="16">
         <v>1627</v>
       </c>
-      <c r="C189" s="17">
+      <c r="C189" s="16">
         <v>15</v>
       </c>
       <c r="D189">
@@ -5358,10 +5412,10 @@
       <c r="A190" s="10">
         <v>2026</v>
       </c>
-      <c r="B190" s="17">
+      <c r="B190" s="16">
         <v>1627</v>
       </c>
-      <c r="C190" s="17">
+      <c r="C190" s="16">
         <v>15</v>
       </c>
       <c r="D190">
@@ -5382,10 +5436,10 @@
       <c r="A191" s="10">
         <v>2026</v>
       </c>
-      <c r="B191" s="17">
+      <c r="B191" s="16">
         <v>1627</v>
       </c>
-      <c r="C191" s="17">
+      <c r="C191" s="16">
         <v>15</v>
       </c>
       <c r="D191">
@@ -5406,10 +5460,10 @@
       <c r="A192" s="10">
         <v>2026</v>
       </c>
-      <c r="B192" s="17">
+      <c r="B192" s="16">
         <v>1627</v>
       </c>
-      <c r="C192" s="17">
+      <c r="C192" s="16">
         <v>15</v>
       </c>
       <c r="D192">
@@ -5430,10 +5484,10 @@
       <c r="A193" s="10">
         <v>2026</v>
       </c>
-      <c r="B193" s="17">
+      <c r="B193" s="16">
         <v>1627</v>
       </c>
-      <c r="C193" s="17">
+      <c r="C193" s="16">
         <v>15</v>
       </c>
       <c r="D193">
@@ -5454,10 +5508,10 @@
       <c r="A194" s="10">
         <v>2026</v>
       </c>
-      <c r="B194" s="17">
+      <c r="B194" s="16">
         <v>1627</v>
       </c>
-      <c r="C194" s="17">
+      <c r="C194" s="16">
         <v>15</v>
       </c>
       <c r="D194">
@@ -5478,10 +5532,10 @@
       <c r="A195" s="10">
         <v>2026</v>
       </c>
-      <c r="B195" s="17">
+      <c r="B195" s="16">
         <v>1627</v>
       </c>
-      <c r="C195" s="17">
+      <c r="C195" s="16">
         <v>15</v>
       </c>
       <c r="D195">
@@ -5502,10 +5556,10 @@
       <c r="A196" s="10">
         <v>2026</v>
       </c>
-      <c r="B196" s="17">
+      <c r="B196" s="16">
         <v>1627</v>
       </c>
-      <c r="C196" s="17">
+      <c r="C196" s="16">
         <v>15</v>
       </c>
       <c r="D196">
@@ -5526,10 +5580,10 @@
       <c r="A197" s="10">
         <v>2026</v>
       </c>
-      <c r="B197" s="16">
+      <c r="B197">
         <v>1628</v>
       </c>
-      <c r="C197" s="16">
+      <c r="C197">
         <v>16</v>
       </c>
       <c r="D197">
@@ -5550,10 +5604,10 @@
       <c r="A198" s="10">
         <v>2026</v>
       </c>
-      <c r="B198" s="16">
+      <c r="B198">
         <v>1628</v>
       </c>
-      <c r="C198" s="16">
+      <c r="C198">
         <v>16</v>
       </c>
       <c r="D198">
@@ -5574,10 +5628,10 @@
       <c r="A199" s="10">
         <v>2026</v>
       </c>
-      <c r="B199" s="16">
+      <c r="B199">
         <v>1628</v>
       </c>
-      <c r="C199" s="16">
+      <c r="C199">
         <v>16</v>
       </c>
       <c r="D199">
@@ -5598,10 +5652,10 @@
       <c r="A200" s="10">
         <v>2026</v>
       </c>
-      <c r="B200" s="16">
+      <c r="B200">
         <v>1628</v>
       </c>
-      <c r="C200" s="16">
+      <c r="C200">
         <v>16</v>
       </c>
       <c r="D200">
@@ -5622,10 +5676,10 @@
       <c r="A201" s="10">
         <v>2026</v>
       </c>
-      <c r="B201" s="16">
+      <c r="B201">
         <v>1628</v>
       </c>
-      <c r="C201" s="16">
+      <c r="C201">
         <v>16</v>
       </c>
       <c r="D201">
@@ -5646,10 +5700,10 @@
       <c r="A202" s="10">
         <v>2026</v>
       </c>
-      <c r="B202" s="16">
+      <c r="B202">
         <v>1628</v>
       </c>
-      <c r="C202" s="16">
+      <c r="C202">
         <v>16</v>
       </c>
       <c r="D202">
@@ -5670,10 +5724,10 @@
       <c r="A203" s="10">
         <v>2026</v>
       </c>
-      <c r="B203" s="16">
+      <c r="B203">
         <v>1628</v>
       </c>
-      <c r="C203" s="16">
+      <c r="C203">
         <v>16</v>
       </c>
       <c r="D203">
@@ -5694,10 +5748,10 @@
       <c r="A204" s="10">
         <v>2026</v>
       </c>
-      <c r="B204" s="16">
+      <c r="B204">
         <v>1628</v>
       </c>
-      <c r="C204" s="16">
+      <c r="C204">
         <v>16</v>
       </c>
       <c r="D204">
@@ -5718,10 +5772,10 @@
       <c r="A205" s="10">
         <v>2026</v>
       </c>
-      <c r="B205" s="16">
+      <c r="B205">
         <v>1628</v>
       </c>
-      <c r="C205" s="16">
+      <c r="C205">
         <v>16</v>
       </c>
       <c r="D205">
@@ -5742,10 +5796,10 @@
       <c r="A206" s="10">
         <v>2026</v>
       </c>
-      <c r="B206" s="16">
+      <c r="B206">
         <v>1628</v>
       </c>
-      <c r="C206" s="16">
+      <c r="C206">
         <v>16</v>
       </c>
       <c r="D206">
@@ -5766,10 +5820,10 @@
       <c r="A207" s="10">
         <v>2026</v>
       </c>
-      <c r="B207" s="16">
+      <c r="B207">
         <v>1628</v>
       </c>
-      <c r="C207" s="16">
+      <c r="C207">
         <v>16</v>
       </c>
       <c r="D207">
@@ -5790,10 +5844,10 @@
       <c r="A208" s="10">
         <v>2026</v>
       </c>
-      <c r="B208" s="16">
+      <c r="B208">
         <v>1628</v>
       </c>
-      <c r="C208" s="16">
+      <c r="C208">
         <v>16</v>
       </c>
       <c r="D208">
@@ -5814,10 +5868,10 @@
       <c r="A209" s="10">
         <v>2026</v>
       </c>
-      <c r="B209" s="16">
+      <c r="B209">
         <v>1628</v>
       </c>
-      <c r="C209" s="16">
+      <c r="C209">
         <v>16</v>
       </c>
       <c r="D209">
@@ -5838,10 +5892,10 @@
       <c r="A210" s="10">
         <v>2026</v>
       </c>
-      <c r="B210" s="18">
+      <c r="B210" s="17">
         <v>1630</v>
       </c>
-      <c r="C210" s="18">
+      <c r="C210" s="17">
         <v>17</v>
       </c>
       <c r="D210">
@@ -5862,10 +5916,10 @@
       <c r="A211" s="10">
         <v>2026</v>
       </c>
-      <c r="B211" s="18">
+      <c r="B211" s="17">
         <v>1630</v>
       </c>
-      <c r="C211" s="18">
+      <c r="C211" s="17">
         <v>17</v>
       </c>
       <c r="D211">
@@ -5886,10 +5940,10 @@
       <c r="A212" s="10">
         <v>2026</v>
       </c>
-      <c r="B212" s="18">
+      <c r="B212" s="17">
         <v>1630</v>
       </c>
-      <c r="C212" s="18">
+      <c r="C212" s="17">
         <v>17</v>
       </c>
       <c r="D212">
@@ -5910,10 +5964,10 @@
       <c r="A213" s="10">
         <v>2026</v>
       </c>
-      <c r="B213" s="18">
+      <c r="B213" s="17">
         <v>1630</v>
       </c>
-      <c r="C213" s="18">
+      <c r="C213" s="17">
         <v>17</v>
       </c>
       <c r="D213">
@@ -5934,10 +5988,10 @@
       <c r="A214" s="10">
         <v>2026</v>
       </c>
-      <c r="B214" s="18">
+      <c r="B214" s="17">
         <v>1630</v>
       </c>
-      <c r="C214" s="18">
+      <c r="C214" s="17">
         <v>17</v>
       </c>
       <c r="D214">
@@ -5958,10 +6012,10 @@
       <c r="A215" s="10">
         <v>2026</v>
       </c>
-      <c r="B215" s="18">
+      <c r="B215" s="17">
         <v>1630</v>
       </c>
-      <c r="C215" s="18">
+      <c r="C215" s="17">
         <v>17</v>
       </c>
       <c r="D215">
@@ -5982,10 +6036,10 @@
       <c r="A216" s="10">
         <v>2026</v>
       </c>
-      <c r="B216" s="18">
+      <c r="B216" s="17">
         <v>1630</v>
       </c>
-      <c r="C216" s="18">
+      <c r="C216" s="17">
         <v>17</v>
       </c>
       <c r="D216">
@@ -6006,10 +6060,10 @@
       <c r="A217" s="10">
         <v>2026</v>
       </c>
-      <c r="B217" s="18">
+      <c r="B217" s="17">
         <v>1630</v>
       </c>
-      <c r="C217" s="18">
+      <c r="C217" s="17">
         <v>17</v>
       </c>
       <c r="D217">
@@ -6030,10 +6084,10 @@
       <c r="A218" s="10">
         <v>2026</v>
       </c>
-      <c r="B218" s="18">
+      <c r="B218" s="17">
         <v>1630</v>
       </c>
-      <c r="C218" s="18">
+      <c r="C218" s="17">
         <v>17</v>
       </c>
       <c r="D218">
@@ -6054,10 +6108,10 @@
       <c r="A219" s="10">
         <v>2026</v>
       </c>
-      <c r="B219" s="18">
+      <c r="B219" s="17">
         <v>1630</v>
       </c>
-      <c r="C219" s="18">
+      <c r="C219" s="17">
         <v>17</v>
       </c>
       <c r="D219">
@@ -6078,10 +6132,10 @@
       <c r="A220" s="10">
         <v>2026</v>
       </c>
-      <c r="B220" s="18">
+      <c r="B220" s="17">
         <v>1630</v>
       </c>
-      <c r="C220" s="18">
+      <c r="C220" s="17">
         <v>17</v>
       </c>
       <c r="D220">
@@ -6102,10 +6156,10 @@
       <c r="A221" s="10">
         <v>2026</v>
       </c>
-      <c r="B221" s="18">
+      <c r="B221" s="17">
         <v>1630</v>
       </c>
-      <c r="C221" s="18">
+      <c r="C221" s="17">
         <v>17</v>
       </c>
       <c r="D221">
@@ -6126,10 +6180,10 @@
       <c r="A222" s="10">
         <v>2026</v>
       </c>
-      <c r="B222" s="18">
+      <c r="B222" s="17">
         <v>1630</v>
       </c>
-      <c r="C222" s="18">
+      <c r="C222" s="17">
         <v>17</v>
       </c>
       <c r="D222">
@@ -6150,10 +6204,10 @@
       <c r="A223" s="10">
         <v>2026</v>
       </c>
-      <c r="B223" s="16">
+      <c r="B223">
         <v>1631</v>
       </c>
-      <c r="C223" s="16">
+      <c r="C223">
         <v>18</v>
       </c>
       <c r="D223">
@@ -6174,10 +6228,10 @@
       <c r="A224" s="10">
         <v>2026</v>
       </c>
-      <c r="B224" s="16">
+      <c r="B224">
         <v>1631</v>
       </c>
-      <c r="C224" s="16">
+      <c r="C224">
         <v>18</v>
       </c>
       <c r="D224">
@@ -6198,10 +6252,10 @@
       <c r="A225" s="10">
         <v>2026</v>
       </c>
-      <c r="B225" s="16">
+      <c r="B225">
         <v>1631</v>
       </c>
-      <c r="C225" s="16">
+      <c r="C225">
         <v>18</v>
       </c>
       <c r="D225">
@@ -6222,10 +6276,10 @@
       <c r="A226" s="10">
         <v>2026</v>
       </c>
-      <c r="B226" s="16">
+      <c r="B226">
         <v>1631</v>
       </c>
-      <c r="C226" s="16">
+      <c r="C226">
         <v>18</v>
       </c>
       <c r="D226">
@@ -6246,10 +6300,10 @@
       <c r="A227" s="10">
         <v>2026</v>
       </c>
-      <c r="B227" s="16">
+      <c r="B227">
         <v>1631</v>
       </c>
-      <c r="C227" s="16">
+      <c r="C227">
         <v>18</v>
       </c>
       <c r="D227">
@@ -6270,10 +6324,10 @@
       <c r="A228" s="10">
         <v>2026</v>
       </c>
-      <c r="B228" s="16">
+      <c r="B228">
         <v>1631</v>
       </c>
-      <c r="C228" s="16">
+      <c r="C228">
         <v>18</v>
       </c>
       <c r="D228">
@@ -6294,10 +6348,10 @@
       <c r="A229" s="10">
         <v>2026</v>
       </c>
-      <c r="B229" s="16">
+      <c r="B229">
         <v>1631</v>
       </c>
-      <c r="C229" s="16">
+      <c r="C229">
         <v>18</v>
       </c>
       <c r="D229">
@@ -6318,10 +6372,10 @@
       <c r="A230" s="10">
         <v>2026</v>
       </c>
-      <c r="B230" s="16">
+      <c r="B230">
         <v>1631</v>
       </c>
-      <c r="C230" s="16">
+      <c r="C230">
         <v>18</v>
       </c>
       <c r="D230">
@@ -6342,10 +6396,10 @@
       <c r="A231" s="10">
         <v>2026</v>
       </c>
-      <c r="B231" s="16">
+      <c r="B231">
         <v>1631</v>
       </c>
-      <c r="C231" s="16">
+      <c r="C231">
         <v>18</v>
       </c>
       <c r="D231">
@@ -6366,10 +6420,10 @@
       <c r="A232" s="10">
         <v>2026</v>
       </c>
-      <c r="B232" s="16">
+      <c r="B232">
         <v>1631</v>
       </c>
-      <c r="C232" s="16">
+      <c r="C232">
         <v>18</v>
       </c>
       <c r="D232">
@@ -6390,10 +6444,10 @@
       <c r="A233" s="10">
         <v>2026</v>
       </c>
-      <c r="B233" s="16">
+      <c r="B233">
         <v>1631</v>
       </c>
-      <c r="C233" s="16">
+      <c r="C233">
         <v>18</v>
       </c>
       <c r="D233">
@@ -6414,10 +6468,10 @@
       <c r="A234" s="10">
         <v>2026</v>
       </c>
-      <c r="B234" s="16">
+      <c r="B234">
         <v>1631</v>
       </c>
-      <c r="C234" s="16">
+      <c r="C234">
         <v>18</v>
       </c>
       <c r="D234">
@@ -6438,10 +6492,10 @@
       <c r="A235" s="10">
         <v>2026</v>
       </c>
-      <c r="B235" s="16">
+      <c r="B235">
         <v>1631</v>
       </c>
-      <c r="C235" s="16">
+      <c r="C235">
         <v>18</v>
       </c>
       <c r="D235">
@@ -6457,6 +6511,2775 @@
         <v>36</v>
       </c>
       <c r="J235" s="14"/>
+    </row>
+    <row r="236" spans="1:10" s="5" customFormat="1">
+      <c r="A236" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B236" s="5">
+        <v>1632</v>
+      </c>
+      <c r="C236" s="5">
+        <v>19</v>
+      </c>
+      <c r="D236" s="5">
+        <v>1</v>
+      </c>
+      <c r="E236" s="18">
+        <v>46172</v>
+      </c>
+      <c r="F236" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G236" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="J236" s="19"/>
+    </row>
+    <row r="237" spans="1:10" s="5" customFormat="1">
+      <c r="A237" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B237" s="5">
+        <v>1632</v>
+      </c>
+      <c r="C237" s="5">
+        <v>19</v>
+      </c>
+      <c r="D237" s="5">
+        <v>2</v>
+      </c>
+      <c r="E237" s="18">
+        <v>46172</v>
+      </c>
+      <c r="F237" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="G237" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J237" s="19"/>
+    </row>
+    <row r="238" spans="1:10" s="5" customFormat="1">
+      <c r="A238" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B238" s="5">
+        <v>1632</v>
+      </c>
+      <c r="C238" s="5">
+        <v>19</v>
+      </c>
+      <c r="D238" s="5">
+        <v>3</v>
+      </c>
+      <c r="E238" s="18">
+        <v>46172</v>
+      </c>
+      <c r="F238" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G238" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J238" s="19"/>
+    </row>
+    <row r="239" spans="1:10" s="5" customFormat="1">
+      <c r="A239" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B239" s="5">
+        <v>1632</v>
+      </c>
+      <c r="C239" s="5">
+        <v>19</v>
+      </c>
+      <c r="D239" s="5">
+        <v>4</v>
+      </c>
+      <c r="E239" s="18">
+        <v>46172</v>
+      </c>
+      <c r="F239" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G239" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J239" s="19"/>
+    </row>
+    <row r="240" spans="1:10" s="5" customFormat="1">
+      <c r="A240" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B240" s="5">
+        <v>1632</v>
+      </c>
+      <c r="C240" s="5">
+        <v>19</v>
+      </c>
+      <c r="D240" s="5">
+        <v>5</v>
+      </c>
+      <c r="E240" s="18">
+        <v>46172</v>
+      </c>
+      <c r="F240" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G240" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J240" s="19"/>
+    </row>
+    <row r="241" spans="1:10" s="5" customFormat="1">
+      <c r="A241" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B241" s="5">
+        <v>1632</v>
+      </c>
+      <c r="C241" s="5">
+        <v>19</v>
+      </c>
+      <c r="D241" s="5">
+        <v>6</v>
+      </c>
+      <c r="E241" s="18">
+        <v>46172</v>
+      </c>
+      <c r="F241" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G241" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J241" s="19"/>
+    </row>
+    <row r="242" spans="1:10" s="5" customFormat="1">
+      <c r="A242" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B242" s="5">
+        <v>1632</v>
+      </c>
+      <c r="C242" s="5">
+        <v>19</v>
+      </c>
+      <c r="D242" s="5">
+        <v>7</v>
+      </c>
+      <c r="E242" s="18">
+        <v>46172</v>
+      </c>
+      <c r="F242" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G242" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="J242" s="19"/>
+    </row>
+    <row r="243" spans="1:10" s="5" customFormat="1">
+      <c r="A243" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B243" s="5">
+        <v>1632</v>
+      </c>
+      <c r="C243" s="5">
+        <v>19</v>
+      </c>
+      <c r="D243" s="5">
+        <v>8</v>
+      </c>
+      <c r="E243" s="18">
+        <v>46173</v>
+      </c>
+      <c r="F243" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G243" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J243" s="19"/>
+    </row>
+    <row r="244" spans="1:10" s="5" customFormat="1">
+      <c r="A244" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B244" s="5">
+        <v>1632</v>
+      </c>
+      <c r="C244" s="5">
+        <v>19</v>
+      </c>
+      <c r="D244" s="5">
+        <v>9</v>
+      </c>
+      <c r="E244" s="18">
+        <v>46173</v>
+      </c>
+      <c r="F244" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G244" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J244" s="19"/>
+    </row>
+    <row r="245" spans="1:10" s="5" customFormat="1">
+      <c r="A245" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B245" s="5">
+        <v>1632</v>
+      </c>
+      <c r="C245" s="5">
+        <v>19</v>
+      </c>
+      <c r="D245" s="5">
+        <v>10</v>
+      </c>
+      <c r="E245" s="18">
+        <v>46172</v>
+      </c>
+      <c r="F245" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G245" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J245" s="19"/>
+    </row>
+    <row r="246" spans="1:10" s="5" customFormat="1">
+      <c r="A246" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B246" s="5">
+        <v>1632</v>
+      </c>
+      <c r="C246" s="5">
+        <v>19</v>
+      </c>
+      <c r="D246" s="5">
+        <v>11</v>
+      </c>
+      <c r="E246" s="18">
+        <v>46172</v>
+      </c>
+      <c r="F246" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G246" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J246" s="19"/>
+    </row>
+    <row r="247" spans="1:10" s="5" customFormat="1">
+      <c r="A247" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B247" s="5">
+        <v>1632</v>
+      </c>
+      <c r="C247" s="5">
+        <v>19</v>
+      </c>
+      <c r="D247" s="5">
+        <v>12</v>
+      </c>
+      <c r="E247" s="18">
+        <v>46172</v>
+      </c>
+      <c r="F247" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G247" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J247" s="19"/>
+    </row>
+    <row r="248" spans="1:10" s="5" customFormat="1" ht="21" thickBot="1">
+      <c r="A248" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B248" s="5">
+        <v>1632</v>
+      </c>
+      <c r="C248" s="5">
+        <v>19</v>
+      </c>
+      <c r="D248" s="5">
+        <v>13</v>
+      </c>
+      <c r="E248" s="18">
+        <v>46173</v>
+      </c>
+      <c r="F248" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G248" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J248" s="19"/>
+    </row>
+    <row r="249" spans="1:10" s="24" customFormat="1" ht="21" thickTop="1">
+      <c r="A249" s="23">
+        <v>2027</v>
+      </c>
+      <c r="B249" s="23">
+        <v>1644</v>
+      </c>
+      <c r="C249" s="23">
+        <v>1</v>
+      </c>
+      <c r="D249" s="24">
+        <v>1</v>
+      </c>
+      <c r="E249" s="25">
+        <v>46242</v>
+      </c>
+      <c r="F249" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G249" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J249" s="26"/>
+    </row>
+    <row r="250" spans="1:10">
+      <c r="A250" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B250" s="15">
+        <v>1644</v>
+      </c>
+      <c r="C250" s="15">
+        <v>1</v>
+      </c>
+      <c r="D250">
+        <v>2</v>
+      </c>
+      <c r="E250" s="13">
+        <v>46242</v>
+      </c>
+      <c r="F250" t="s">
+        <v>25</v>
+      </c>
+      <c r="G250" t="s">
+        <v>28</v>
+      </c>
+      <c r="J250" s="14"/>
+    </row>
+    <row r="251" spans="1:10">
+      <c r="A251" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B251" s="15">
+        <v>1644</v>
+      </c>
+      <c r="C251" s="15">
+        <v>1</v>
+      </c>
+      <c r="D251">
+        <v>3</v>
+      </c>
+      <c r="E251" s="13">
+        <v>46242</v>
+      </c>
+      <c r="F251" t="s">
+        <v>29</v>
+      </c>
+      <c r="G251" t="s">
+        <v>30</v>
+      </c>
+      <c r="J251" s="14"/>
+    </row>
+    <row r="252" spans="1:10">
+      <c r="A252" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B252" s="15">
+        <v>1644</v>
+      </c>
+      <c r="C252" s="15">
+        <v>1</v>
+      </c>
+      <c r="D252">
+        <v>4</v>
+      </c>
+      <c r="E252" s="13">
+        <v>46242</v>
+      </c>
+      <c r="F252" t="s">
+        <v>27</v>
+      </c>
+      <c r="G252" t="s">
+        <v>51</v>
+      </c>
+      <c r="J252" s="14"/>
+    </row>
+    <row r="253" spans="1:10">
+      <c r="A253" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B253" s="15">
+        <v>1644</v>
+      </c>
+      <c r="C253" s="15">
+        <v>1</v>
+      </c>
+      <c r="D253">
+        <v>5</v>
+      </c>
+      <c r="E253" s="13">
+        <v>46242</v>
+      </c>
+      <c r="F253" t="s">
+        <v>45</v>
+      </c>
+      <c r="G253" t="s">
+        <v>22</v>
+      </c>
+      <c r="J253" s="14"/>
+    </row>
+    <row r="254" spans="1:10">
+      <c r="A254" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B254" s="15">
+        <v>1644</v>
+      </c>
+      <c r="C254" s="15">
+        <v>1</v>
+      </c>
+      <c r="D254">
+        <v>6</v>
+      </c>
+      <c r="E254" s="13">
+        <v>46242</v>
+      </c>
+      <c r="F254" t="s">
+        <v>32</v>
+      </c>
+      <c r="G254" t="s">
+        <v>34</v>
+      </c>
+      <c r="J254" s="14"/>
+    </row>
+    <row r="255" spans="1:10">
+      <c r="A255" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B255" s="15">
+        <v>1644</v>
+      </c>
+      <c r="C255" s="15">
+        <v>1</v>
+      </c>
+      <c r="D255">
+        <v>7</v>
+      </c>
+      <c r="E255" s="13">
+        <v>46243</v>
+      </c>
+      <c r="F255" t="s">
+        <v>33</v>
+      </c>
+      <c r="G255" t="s">
+        <v>31</v>
+      </c>
+      <c r="J255" s="14"/>
+    </row>
+    <row r="256" spans="1:10">
+      <c r="A256" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B256" s="15">
+        <v>1644</v>
+      </c>
+      <c r="C256" s="15">
+        <v>1</v>
+      </c>
+      <c r="D256">
+        <v>8</v>
+      </c>
+      <c r="E256" s="13">
+        <v>46243</v>
+      </c>
+      <c r="F256" t="s">
+        <v>52</v>
+      </c>
+      <c r="G256" t="s">
+        <v>49</v>
+      </c>
+      <c r="J256" s="14"/>
+    </row>
+    <row r="257" spans="1:10">
+      <c r="A257" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B257" s="15">
+        <v>1644</v>
+      </c>
+      <c r="C257" s="15">
+        <v>1</v>
+      </c>
+      <c r="D257">
+        <v>9</v>
+      </c>
+      <c r="E257" s="13">
+        <v>46242</v>
+      </c>
+      <c r="F257" t="s">
+        <v>38</v>
+      </c>
+      <c r="G257" t="s">
+        <v>46</v>
+      </c>
+      <c r="J257" s="14"/>
+    </row>
+    <row r="258" spans="1:10">
+      <c r="A258" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B258" s="15">
+        <v>1644</v>
+      </c>
+      <c r="C258" s="15">
+        <v>1</v>
+      </c>
+      <c r="D258">
+        <v>10</v>
+      </c>
+      <c r="E258" s="13">
+        <v>46242</v>
+      </c>
+      <c r="F258" t="s">
+        <v>56</v>
+      </c>
+      <c r="G258" t="s">
+        <v>35</v>
+      </c>
+      <c r="J258" s="14"/>
+    </row>
+    <row r="259" spans="1:10">
+      <c r="A259" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B259" s="15">
+        <v>1644</v>
+      </c>
+      <c r="C259" s="15">
+        <v>1</v>
+      </c>
+      <c r="D259">
+        <v>11</v>
+      </c>
+      <c r="E259" s="13">
+        <v>46242</v>
+      </c>
+      <c r="F259" t="s">
+        <v>57</v>
+      </c>
+      <c r="G259" t="s">
+        <v>54</v>
+      </c>
+      <c r="J259" s="14"/>
+    </row>
+    <row r="260" spans="1:10">
+      <c r="A260" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B260" s="15">
+        <v>1644</v>
+      </c>
+      <c r="C260" s="15">
+        <v>1</v>
+      </c>
+      <c r="D260">
+        <v>12</v>
+      </c>
+      <c r="E260" s="13">
+        <v>46243</v>
+      </c>
+      <c r="F260" t="s">
+        <v>40</v>
+      </c>
+      <c r="G260" t="s">
+        <v>43</v>
+      </c>
+      <c r="J260" s="14"/>
+    </row>
+    <row r="261" spans="1:10">
+      <c r="A261" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B261" s="15">
+        <v>1644</v>
+      </c>
+      <c r="C261" s="15">
+        <v>1</v>
+      </c>
+      <c r="D261">
+        <v>13</v>
+      </c>
+      <c r="E261" s="13">
+        <v>46243</v>
+      </c>
+      <c r="F261" t="s">
+        <v>36</v>
+      </c>
+      <c r="G261" t="s">
+        <v>64</v>
+      </c>
+      <c r="J261" s="14"/>
+    </row>
+    <row r="262" spans="1:10">
+      <c r="A262" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B262" s="20">
+        <v>1645</v>
+      </c>
+      <c r="C262" s="20">
+        <v>2</v>
+      </c>
+      <c r="D262" s="20">
+        <v>1</v>
+      </c>
+      <c r="E262" s="21">
+        <v>46249</v>
+      </c>
+      <c r="F262" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G262" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10">
+      <c r="A263" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B263" s="20">
+        <v>1645</v>
+      </c>
+      <c r="C263" s="20">
+        <v>2</v>
+      </c>
+      <c r="D263" s="20">
+        <v>2</v>
+      </c>
+      <c r="E263" s="21">
+        <v>46249</v>
+      </c>
+      <c r="F263" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G263" s="20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10">
+      <c r="A264" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B264" s="20">
+        <v>1645</v>
+      </c>
+      <c r="C264" s="20">
+        <v>2</v>
+      </c>
+      <c r="D264" s="20">
+        <v>3</v>
+      </c>
+      <c r="E264" s="21">
+        <v>46249</v>
+      </c>
+      <c r="F264" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="G264" s="20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10">
+      <c r="A265" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B265" s="20">
+        <v>1645</v>
+      </c>
+      <c r="C265" s="20">
+        <v>2</v>
+      </c>
+      <c r="D265" s="20">
+        <v>4</v>
+      </c>
+      <c r="E265" s="21">
+        <v>46249</v>
+      </c>
+      <c r="F265" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G265" s="20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10">
+      <c r="A266" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B266" s="20">
+        <v>1645</v>
+      </c>
+      <c r="C266" s="20">
+        <v>2</v>
+      </c>
+      <c r="D266" s="20">
+        <v>5</v>
+      </c>
+      <c r="E266" s="21">
+        <v>46249</v>
+      </c>
+      <c r="F266" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G266" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10">
+      <c r="A267" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B267" s="20">
+        <v>1645</v>
+      </c>
+      <c r="C267" s="20">
+        <v>2</v>
+      </c>
+      <c r="D267" s="20">
+        <v>6</v>
+      </c>
+      <c r="E267" s="21">
+        <v>46249</v>
+      </c>
+      <c r="F267" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G267" s="20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10">
+      <c r="A268" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B268" s="20">
+        <v>1645</v>
+      </c>
+      <c r="C268" s="20">
+        <v>2</v>
+      </c>
+      <c r="D268" s="20">
+        <v>7</v>
+      </c>
+      <c r="E268" s="21">
+        <v>46249</v>
+      </c>
+      <c r="F268" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G268" s="20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10">
+      <c r="A269" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B269" s="20">
+        <v>1645</v>
+      </c>
+      <c r="C269" s="20">
+        <v>2</v>
+      </c>
+      <c r="D269" s="20">
+        <v>8</v>
+      </c>
+      <c r="E269" s="21">
+        <v>46249</v>
+      </c>
+      <c r="F269" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G269" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10">
+      <c r="A270" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B270" s="20">
+        <v>1645</v>
+      </c>
+      <c r="C270" s="20">
+        <v>2</v>
+      </c>
+      <c r="D270" s="20">
+        <v>9</v>
+      </c>
+      <c r="E270" s="21">
+        <v>46249</v>
+      </c>
+      <c r="F270" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="G270" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10">
+      <c r="A271" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B271" s="20">
+        <v>1645</v>
+      </c>
+      <c r="C271" s="20">
+        <v>2</v>
+      </c>
+      <c r="D271" s="20">
+        <v>10</v>
+      </c>
+      <c r="E271" s="21">
+        <v>46249</v>
+      </c>
+      <c r="F271" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G271" s="20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10">
+      <c r="A272" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B272" s="20">
+        <v>1645</v>
+      </c>
+      <c r="C272" s="20">
+        <v>2</v>
+      </c>
+      <c r="D272" s="20">
+        <v>11</v>
+      </c>
+      <c r="E272" s="21">
+        <v>46249</v>
+      </c>
+      <c r="F272" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G272" s="20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B273" s="20">
+        <v>1645</v>
+      </c>
+      <c r="C273" s="20">
+        <v>2</v>
+      </c>
+      <c r="D273" s="20">
+        <v>12</v>
+      </c>
+      <c r="E273" s="21">
+        <v>46249</v>
+      </c>
+      <c r="F273" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G273" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B274" s="20">
+        <v>1645</v>
+      </c>
+      <c r="C274" s="20">
+        <v>2</v>
+      </c>
+      <c r="D274" s="20">
+        <v>13</v>
+      </c>
+      <c r="E274" s="21">
+        <v>46249</v>
+      </c>
+      <c r="F274" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="G274" s="20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B275" s="16">
+        <v>1647</v>
+      </c>
+      <c r="C275" s="16">
+        <v>3</v>
+      </c>
+      <c r="D275">
+        <v>1</v>
+      </c>
+      <c r="E275" s="13">
+        <v>46256</v>
+      </c>
+      <c r="F275" t="s">
+        <v>24</v>
+      </c>
+      <c r="G275" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B276" s="16">
+        <v>1647</v>
+      </c>
+      <c r="C276" s="16">
+        <v>3</v>
+      </c>
+      <c r="D276">
+        <v>2</v>
+      </c>
+      <c r="E276" s="13">
+        <v>46256</v>
+      </c>
+      <c r="F276" t="s">
+        <v>28</v>
+      </c>
+      <c r="G276" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B277" s="16">
+        <v>1647</v>
+      </c>
+      <c r="C277" s="16">
+        <v>3</v>
+      </c>
+      <c r="D277">
+        <v>3</v>
+      </c>
+      <c r="E277" s="13">
+        <v>46256</v>
+      </c>
+      <c r="F277" t="s">
+        <v>29</v>
+      </c>
+      <c r="G277" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B278" s="16">
+        <v>1647</v>
+      </c>
+      <c r="C278" s="16">
+        <v>3</v>
+      </c>
+      <c r="D278">
+        <v>4</v>
+      </c>
+      <c r="E278" s="13">
+        <v>46256</v>
+      </c>
+      <c r="F278" t="s">
+        <v>49</v>
+      </c>
+      <c r="G278" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B279" s="16">
+        <v>1647</v>
+      </c>
+      <c r="C279" s="16">
+        <v>3</v>
+      </c>
+      <c r="D279">
+        <v>5</v>
+      </c>
+      <c r="E279" s="13">
+        <v>46256</v>
+      </c>
+      <c r="F279" t="s">
+        <v>45</v>
+      </c>
+      <c r="G279" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B280" s="16">
+        <v>1647</v>
+      </c>
+      <c r="C280" s="16">
+        <v>3</v>
+      </c>
+      <c r="D280">
+        <v>6</v>
+      </c>
+      <c r="E280" s="13">
+        <v>46256</v>
+      </c>
+      <c r="F280" t="s">
+        <v>25</v>
+      </c>
+      <c r="G280" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B281" s="16">
+        <v>1647</v>
+      </c>
+      <c r="C281" s="16">
+        <v>3</v>
+      </c>
+      <c r="D281">
+        <v>7</v>
+      </c>
+      <c r="E281" s="13">
+        <v>46256</v>
+      </c>
+      <c r="F281" t="s">
+        <v>50</v>
+      </c>
+      <c r="G281" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B282" s="16">
+        <v>1647</v>
+      </c>
+      <c r="C282" s="16">
+        <v>3</v>
+      </c>
+      <c r="D282">
+        <v>8</v>
+      </c>
+      <c r="E282" s="13">
+        <v>46256</v>
+      </c>
+      <c r="F282" t="s">
+        <v>38</v>
+      </c>
+      <c r="G282" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B283" s="16">
+        <v>1647</v>
+      </c>
+      <c r="C283" s="16">
+        <v>3</v>
+      </c>
+      <c r="D283">
+        <v>9</v>
+      </c>
+      <c r="E283" s="13">
+        <v>46256</v>
+      </c>
+      <c r="F283" t="s">
+        <v>40</v>
+      </c>
+      <c r="G283" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B284" s="16">
+        <v>1647</v>
+      </c>
+      <c r="C284" s="16">
+        <v>3</v>
+      </c>
+      <c r="D284">
+        <v>10</v>
+      </c>
+      <c r="E284" s="13">
+        <v>46256</v>
+      </c>
+      <c r="F284" t="s">
+        <v>58</v>
+      </c>
+      <c r="G284" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B285" s="16">
+        <v>1647</v>
+      </c>
+      <c r="C285" s="16">
+        <v>3</v>
+      </c>
+      <c r="D285">
+        <v>11</v>
+      </c>
+      <c r="E285" s="13">
+        <v>46256</v>
+      </c>
+      <c r="F285" t="s">
+        <v>57</v>
+      </c>
+      <c r="G285" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B286" s="16">
+        <v>1647</v>
+      </c>
+      <c r="C286" s="16">
+        <v>3</v>
+      </c>
+      <c r="D286">
+        <v>12</v>
+      </c>
+      <c r="E286" s="13">
+        <v>46256</v>
+      </c>
+      <c r="F286" t="s">
+        <v>41</v>
+      </c>
+      <c r="G286" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B287" s="16">
+        <v>1647</v>
+      </c>
+      <c r="C287" s="16">
+        <v>3</v>
+      </c>
+      <c r="D287">
+        <v>13</v>
+      </c>
+      <c r="E287" s="13">
+        <v>46256</v>
+      </c>
+      <c r="F287" t="s">
+        <v>39</v>
+      </c>
+      <c r="G287" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B288" s="17">
+        <v>1648</v>
+      </c>
+      <c r="C288" s="17">
+        <v>4</v>
+      </c>
+      <c r="D288" s="17">
+        <v>1</v>
+      </c>
+      <c r="E288" s="22">
+        <v>46263</v>
+      </c>
+      <c r="F288" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="G288" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7">
+      <c r="A289" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B289" s="17">
+        <v>1648</v>
+      </c>
+      <c r="C289" s="17">
+        <v>4</v>
+      </c>
+      <c r="D289" s="17">
+        <v>2</v>
+      </c>
+      <c r="E289" s="22">
+        <v>46263</v>
+      </c>
+      <c r="F289" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G289" s="17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7">
+      <c r="A290" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B290" s="17">
+        <v>1648</v>
+      </c>
+      <c r="C290" s="17">
+        <v>4</v>
+      </c>
+      <c r="D290" s="17">
+        <v>3</v>
+      </c>
+      <c r="E290" s="22">
+        <v>46263</v>
+      </c>
+      <c r="F290" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="G290" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B291" s="17">
+        <v>1648</v>
+      </c>
+      <c r="C291" s="17">
+        <v>4</v>
+      </c>
+      <c r="D291" s="17">
+        <v>4</v>
+      </c>
+      <c r="E291" s="22">
+        <v>46263</v>
+      </c>
+      <c r="F291" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G291" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B292" s="17">
+        <v>1648</v>
+      </c>
+      <c r="C292" s="17">
+        <v>4</v>
+      </c>
+      <c r="D292" s="17">
+        <v>5</v>
+      </c>
+      <c r="E292" s="22">
+        <v>46263</v>
+      </c>
+      <c r="F292" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G292" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7">
+      <c r="A293" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B293" s="17">
+        <v>1648</v>
+      </c>
+      <c r="C293" s="17">
+        <v>4</v>
+      </c>
+      <c r="D293" s="17">
+        <v>6</v>
+      </c>
+      <c r="E293" s="22">
+        <v>46263</v>
+      </c>
+      <c r="F293" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G293" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7">
+      <c r="A294" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B294" s="17">
+        <v>1648</v>
+      </c>
+      <c r="C294" s="17">
+        <v>4</v>
+      </c>
+      <c r="D294" s="17">
+        <v>7</v>
+      </c>
+      <c r="E294" s="22">
+        <v>46263</v>
+      </c>
+      <c r="F294" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G294" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B295" s="17">
+        <v>1648</v>
+      </c>
+      <c r="C295" s="17">
+        <v>4</v>
+      </c>
+      <c r="D295" s="17">
+        <v>8</v>
+      </c>
+      <c r="E295" s="22">
+        <v>46263</v>
+      </c>
+      <c r="F295" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G295" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B296" s="17">
+        <v>1648</v>
+      </c>
+      <c r="C296" s="17">
+        <v>4</v>
+      </c>
+      <c r="D296" s="17">
+        <v>9</v>
+      </c>
+      <c r="E296" s="22">
+        <v>46263</v>
+      </c>
+      <c r="F296" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="G296" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B297" s="17">
+        <v>1648</v>
+      </c>
+      <c r="C297" s="17">
+        <v>4</v>
+      </c>
+      <c r="D297" s="17">
+        <v>10</v>
+      </c>
+      <c r="E297" s="22">
+        <v>46263</v>
+      </c>
+      <c r="F297" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G297" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B298" s="17">
+        <v>1648</v>
+      </c>
+      <c r="C298" s="17">
+        <v>4</v>
+      </c>
+      <c r="D298" s="17">
+        <v>11</v>
+      </c>
+      <c r="E298" s="22">
+        <v>46263</v>
+      </c>
+      <c r="F298" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G298" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7">
+      <c r="A299" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B299" s="17">
+        <v>1648</v>
+      </c>
+      <c r="C299" s="17">
+        <v>4</v>
+      </c>
+      <c r="D299" s="17">
+        <v>12</v>
+      </c>
+      <c r="E299" s="22">
+        <v>46263</v>
+      </c>
+      <c r="F299" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="G299" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B300" s="17">
+        <v>1648</v>
+      </c>
+      <c r="C300" s="17">
+        <v>4</v>
+      </c>
+      <c r="D300" s="17">
+        <v>13</v>
+      </c>
+      <c r="E300" s="22">
+        <v>46263</v>
+      </c>
+      <c r="F300" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G300" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7">
+      <c r="A301" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B301" s="15">
+        <v>1649</v>
+      </c>
+      <c r="C301" s="15">
+        <v>5</v>
+      </c>
+      <c r="D301">
+        <v>1</v>
+      </c>
+      <c r="E301" s="13">
+        <v>46267</v>
+      </c>
+      <c r="F301" t="s">
+        <v>33</v>
+      </c>
+      <c r="G301" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
+      <c r="A302" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B302" s="15">
+        <v>1649</v>
+      </c>
+      <c r="C302" s="15">
+        <v>5</v>
+      </c>
+      <c r="D302">
+        <v>2</v>
+      </c>
+      <c r="E302" s="13">
+        <v>46267</v>
+      </c>
+      <c r="F302" t="s">
+        <v>25</v>
+      </c>
+      <c r="G302" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7">
+      <c r="A303" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B303" s="15">
+        <v>1649</v>
+      </c>
+      <c r="C303" s="15">
+        <v>5</v>
+      </c>
+      <c r="D303">
+        <v>3</v>
+      </c>
+      <c r="E303" s="13">
+        <v>46267</v>
+      </c>
+      <c r="F303" t="s">
+        <v>45</v>
+      </c>
+      <c r="G303" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7">
+      <c r="A304" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B304" s="15">
+        <v>1649</v>
+      </c>
+      <c r="C304" s="15">
+        <v>5</v>
+      </c>
+      <c r="D304">
+        <v>4</v>
+      </c>
+      <c r="E304" s="13">
+        <v>46267</v>
+      </c>
+      <c r="F304" t="s">
+        <v>22</v>
+      </c>
+      <c r="G304" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7">
+      <c r="A305" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B305" s="15">
+        <v>1649</v>
+      </c>
+      <c r="C305" s="15">
+        <v>5</v>
+      </c>
+      <c r="D305">
+        <v>5</v>
+      </c>
+      <c r="E305" s="13">
+        <v>46267</v>
+      </c>
+      <c r="F305" t="s">
+        <v>27</v>
+      </c>
+      <c r="G305" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7">
+      <c r="A306" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B306" s="15">
+        <v>1649</v>
+      </c>
+      <c r="C306" s="15">
+        <v>5</v>
+      </c>
+      <c r="D306">
+        <v>6</v>
+      </c>
+      <c r="E306" s="13">
+        <v>46267</v>
+      </c>
+      <c r="F306" t="s">
+        <v>34</v>
+      </c>
+      <c r="G306" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7">
+      <c r="A307" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B307" s="15">
+        <v>1649</v>
+      </c>
+      <c r="C307" s="15">
+        <v>5</v>
+      </c>
+      <c r="D307">
+        <v>7</v>
+      </c>
+      <c r="E307" s="13">
+        <v>46267</v>
+      </c>
+      <c r="F307" t="s">
+        <v>44</v>
+      </c>
+      <c r="G307" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7">
+      <c r="A308" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B308" s="15">
+        <v>1649</v>
+      </c>
+      <c r="C308" s="15">
+        <v>5</v>
+      </c>
+      <c r="D308">
+        <v>8</v>
+      </c>
+      <c r="E308" s="13">
+        <v>46267</v>
+      </c>
+      <c r="F308" t="s">
+        <v>50</v>
+      </c>
+      <c r="G308" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7">
+      <c r="A309" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B309" s="15">
+        <v>1649</v>
+      </c>
+      <c r="C309" s="15">
+        <v>5</v>
+      </c>
+      <c r="D309">
+        <v>9</v>
+      </c>
+      <c r="E309" s="13">
+        <v>46267</v>
+      </c>
+      <c r="F309" t="s">
+        <v>30</v>
+      </c>
+      <c r="G309" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7">
+      <c r="A310" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B310" s="15">
+        <v>1649</v>
+      </c>
+      <c r="C310" s="15">
+        <v>5</v>
+      </c>
+      <c r="D310">
+        <v>10</v>
+      </c>
+      <c r="E310" s="13">
+        <v>46267</v>
+      </c>
+      <c r="F310" t="s">
+        <v>52</v>
+      </c>
+      <c r="G310" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7">
+      <c r="A311" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B311" s="15">
+        <v>1649</v>
+      </c>
+      <c r="C311" s="15">
+        <v>5</v>
+      </c>
+      <c r="D311">
+        <v>11</v>
+      </c>
+      <c r="E311" s="13">
+        <v>46267</v>
+      </c>
+      <c r="F311" t="s">
+        <v>53</v>
+      </c>
+      <c r="G311" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7">
+      <c r="A312" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B312" s="15">
+        <v>1649</v>
+      </c>
+      <c r="C312" s="15">
+        <v>5</v>
+      </c>
+      <c r="D312">
+        <v>12</v>
+      </c>
+      <c r="E312" s="13">
+        <v>46267</v>
+      </c>
+      <c r="F312" t="s">
+        <v>16</v>
+      </c>
+      <c r="G312" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7">
+      <c r="A313" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B313" s="15">
+        <v>1649</v>
+      </c>
+      <c r="C313" s="15">
+        <v>5</v>
+      </c>
+      <c r="D313">
+        <v>13</v>
+      </c>
+      <c r="E313" s="13">
+        <v>46267</v>
+      </c>
+      <c r="F313" t="s">
+        <v>61</v>
+      </c>
+      <c r="G313" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7">
+      <c r="A314" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B314" s="20">
+        <v>1650</v>
+      </c>
+      <c r="C314" s="20">
+        <v>6</v>
+      </c>
+      <c r="D314" s="20">
+        <v>1</v>
+      </c>
+      <c r="E314" s="21">
+        <v>46270</v>
+      </c>
+      <c r="F314" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G314" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7">
+      <c r="A315" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B315" s="20">
+        <v>1650</v>
+      </c>
+      <c r="C315" s="20">
+        <v>6</v>
+      </c>
+      <c r="D315" s="20">
+        <v>2</v>
+      </c>
+      <c r="E315" s="21">
+        <v>46271</v>
+      </c>
+      <c r="F315" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G315" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7">
+      <c r="A316" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B316" s="20">
+        <v>1650</v>
+      </c>
+      <c r="C316" s="20">
+        <v>6</v>
+      </c>
+      <c r="D316" s="20">
+        <v>3</v>
+      </c>
+      <c r="E316" s="21">
+        <v>46271</v>
+      </c>
+      <c r="F316" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G316" s="20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7">
+      <c r="A317" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B317" s="20">
+        <v>1650</v>
+      </c>
+      <c r="C317" s="20">
+        <v>6</v>
+      </c>
+      <c r="D317" s="20">
+        <v>4</v>
+      </c>
+      <c r="E317" s="21">
+        <v>46271</v>
+      </c>
+      <c r="F317" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G317" s="20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7">
+      <c r="A318" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B318" s="20">
+        <v>1650</v>
+      </c>
+      <c r="C318" s="20">
+        <v>6</v>
+      </c>
+      <c r="D318" s="20">
+        <v>5</v>
+      </c>
+      <c r="E318" s="21">
+        <v>46271</v>
+      </c>
+      <c r="F318" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="G318" s="20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7">
+      <c r="A319" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B319" s="20">
+        <v>1650</v>
+      </c>
+      <c r="C319" s="20">
+        <v>6</v>
+      </c>
+      <c r="D319" s="20">
+        <v>6</v>
+      </c>
+      <c r="E319" s="21">
+        <v>46271</v>
+      </c>
+      <c r="F319" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G319" s="20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7">
+      <c r="A320" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B320" s="20">
+        <v>1650</v>
+      </c>
+      <c r="C320" s="20">
+        <v>6</v>
+      </c>
+      <c r="D320" s="20">
+        <v>7</v>
+      </c>
+      <c r="E320" s="21">
+        <v>46271</v>
+      </c>
+      <c r="F320" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G320" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10">
+      <c r="A321" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B321" s="20">
+        <v>1650</v>
+      </c>
+      <c r="C321" s="20">
+        <v>6</v>
+      </c>
+      <c r="D321" s="20">
+        <v>8</v>
+      </c>
+      <c r="E321" s="21">
+        <v>46271</v>
+      </c>
+      <c r="F321" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="G321" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="322" spans="1:10">
+      <c r="A322" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B322" s="20">
+        <v>1650</v>
+      </c>
+      <c r="C322" s="20">
+        <v>6</v>
+      </c>
+      <c r="D322" s="20">
+        <v>9</v>
+      </c>
+      <c r="E322" s="21">
+        <v>46271</v>
+      </c>
+      <c r="F322" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G322" s="20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="323" spans="1:10">
+      <c r="A323" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B323" s="20">
+        <v>1650</v>
+      </c>
+      <c r="C323" s="20">
+        <v>6</v>
+      </c>
+      <c r="D323" s="20">
+        <v>10</v>
+      </c>
+      <c r="E323" s="21">
+        <v>46271</v>
+      </c>
+      <c r="F323" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G323" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="324" spans="1:10">
+      <c r="A324" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B324" s="20">
+        <v>1650</v>
+      </c>
+      <c r="C324" s="20">
+        <v>6</v>
+      </c>
+      <c r="D324" s="20">
+        <v>11</v>
+      </c>
+      <c r="E324" s="21">
+        <v>46270</v>
+      </c>
+      <c r="F324" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G324" s="20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="325" spans="1:10">
+      <c r="A325" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B325" s="20">
+        <v>1650</v>
+      </c>
+      <c r="C325" s="20">
+        <v>6</v>
+      </c>
+      <c r="D325" s="20">
+        <v>12</v>
+      </c>
+      <c r="E325" s="21">
+        <v>46270</v>
+      </c>
+      <c r="F325" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="G325" s="20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="326" spans="1:10">
+      <c r="A326" s="20">
+        <v>2027</v>
+      </c>
+      <c r="B326" s="20">
+        <v>1650</v>
+      </c>
+      <c r="C326" s="20">
+        <v>6</v>
+      </c>
+      <c r="D326" s="20">
+        <v>13</v>
+      </c>
+      <c r="E326" s="21">
+        <v>46271</v>
+      </c>
+      <c r="F326" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="G326" s="20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="327" spans="1:10">
+      <c r="A327" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B327" s="16">
+        <v>1653</v>
+      </c>
+      <c r="C327" s="16">
+        <v>7</v>
+      </c>
+      <c r="D327" s="16">
+        <v>1</v>
+      </c>
+      <c r="E327" s="27">
+        <v>46277</v>
+      </c>
+      <c r="F327" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G327" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="I327" s="13"/>
+      <c r="J327" s="14"/>
+    </row>
+    <row r="328" spans="1:10">
+      <c r="A328" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B328" s="16">
+        <v>1653</v>
+      </c>
+      <c r="C328" s="16">
+        <v>7</v>
+      </c>
+      <c r="D328" s="16">
+        <v>2</v>
+      </c>
+      <c r="E328" s="27">
+        <v>46277</v>
+      </c>
+      <c r="F328" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G328" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I328" s="13"/>
+      <c r="J328" s="14"/>
+    </row>
+    <row r="329" spans="1:10">
+      <c r="A329" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B329" s="16">
+        <v>1653</v>
+      </c>
+      <c r="C329" s="16">
+        <v>7</v>
+      </c>
+      <c r="D329" s="16">
+        <v>3</v>
+      </c>
+      <c r="E329" s="27">
+        <v>46277</v>
+      </c>
+      <c r="F329" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G329" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I329" s="13"/>
+      <c r="J329" s="14"/>
+    </row>
+    <row r="330" spans="1:10">
+      <c r="A330" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B330" s="16">
+        <v>1653</v>
+      </c>
+      <c r="C330" s="16">
+        <v>7</v>
+      </c>
+      <c r="D330" s="16">
+        <v>4</v>
+      </c>
+      <c r="E330" s="27">
+        <v>46277</v>
+      </c>
+      <c r="F330" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G330" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="I330" s="13"/>
+      <c r="J330" s="14"/>
+    </row>
+    <row r="331" spans="1:10">
+      <c r="A331" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B331" s="16">
+        <v>1653</v>
+      </c>
+      <c r="C331" s="16">
+        <v>7</v>
+      </c>
+      <c r="D331" s="16">
+        <v>5</v>
+      </c>
+      <c r="E331" s="27">
+        <v>46277</v>
+      </c>
+      <c r="F331" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G331" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="I331" s="13"/>
+      <c r="J331" s="14"/>
+    </row>
+    <row r="332" spans="1:10">
+      <c r="A332" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B332" s="16">
+        <v>1653</v>
+      </c>
+      <c r="C332" s="16">
+        <v>7</v>
+      </c>
+      <c r="D332" s="16">
+        <v>6</v>
+      </c>
+      <c r="E332" s="27">
+        <v>46277</v>
+      </c>
+      <c r="F332" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G332" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="I332" s="13"/>
+      <c r="J332" s="14"/>
+    </row>
+    <row r="333" spans="1:10">
+      <c r="A333" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B333" s="16">
+        <v>1653</v>
+      </c>
+      <c r="C333" s="16">
+        <v>7</v>
+      </c>
+      <c r="D333" s="16">
+        <v>7</v>
+      </c>
+      <c r="E333" s="27">
+        <v>46278</v>
+      </c>
+      <c r="F333" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G333" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="I333" s="13"/>
+      <c r="J333" s="14"/>
+    </row>
+    <row r="334" spans="1:10">
+      <c r="A334" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B334" s="16">
+        <v>1653</v>
+      </c>
+      <c r="C334" s="16">
+        <v>7</v>
+      </c>
+      <c r="D334" s="16">
+        <v>8</v>
+      </c>
+      <c r="E334" s="27">
+        <v>46278</v>
+      </c>
+      <c r="F334" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G334" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="I334" s="13"/>
+      <c r="J334" s="14"/>
+    </row>
+    <row r="335" spans="1:10">
+      <c r="A335" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B335" s="16">
+        <v>1653</v>
+      </c>
+      <c r="C335" s="16">
+        <v>7</v>
+      </c>
+      <c r="D335" s="16">
+        <v>9</v>
+      </c>
+      <c r="E335" s="27">
+        <v>46277</v>
+      </c>
+      <c r="F335" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G335" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="I335" s="13"/>
+      <c r="J335" s="14"/>
+    </row>
+    <row r="336" spans="1:10">
+      <c r="A336" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B336" s="16">
+        <v>1653</v>
+      </c>
+      <c r="C336" s="16">
+        <v>7</v>
+      </c>
+      <c r="D336" s="16">
+        <v>10</v>
+      </c>
+      <c r="E336" s="27">
+        <v>46277</v>
+      </c>
+      <c r="F336" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="G336" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="I336" s="13"/>
+      <c r="J336" s="14"/>
+    </row>
+    <row r="337" spans="1:10">
+      <c r="A337" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B337" s="16">
+        <v>1653</v>
+      </c>
+      <c r="C337" s="16">
+        <v>7</v>
+      </c>
+      <c r="D337" s="16">
+        <v>11</v>
+      </c>
+      <c r="E337" s="27">
+        <v>46277</v>
+      </c>
+      <c r="F337" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G337" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="I337" s="13"/>
+      <c r="J337" s="14"/>
+    </row>
+    <row r="338" spans="1:10">
+      <c r="A338" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B338" s="16">
+        <v>1653</v>
+      </c>
+      <c r="C338" s="16">
+        <v>7</v>
+      </c>
+      <c r="D338" s="16">
+        <v>12</v>
+      </c>
+      <c r="E338" s="27">
+        <v>46277</v>
+      </c>
+      <c r="F338" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G338" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="I338" s="13"/>
+      <c r="J338" s="14"/>
+    </row>
+    <row r="339" spans="1:10">
+      <c r="A339" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B339" s="16">
+        <v>1653</v>
+      </c>
+      <c r="C339" s="16">
+        <v>7</v>
+      </c>
+      <c r="D339" s="16">
+        <v>13</v>
+      </c>
+      <c r="E339" s="27">
+        <v>46277</v>
+      </c>
+      <c r="F339" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="G339" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="I339" s="13"/>
+      <c r="J339" s="14"/>
+    </row>
+    <row r="340" spans="1:10">
+      <c r="A340" s="28">
+        <v>2027</v>
+      </c>
+      <c r="B340" s="28">
+        <v>1654</v>
+      </c>
+      <c r="C340" s="28">
+        <v>8</v>
+      </c>
+      <c r="D340" s="28">
+        <v>1</v>
+      </c>
+      <c r="E340" s="29">
+        <v>46284</v>
+      </c>
+      <c r="F340" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="G340" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="I340" s="13"/>
+      <c r="J340" s="14"/>
+    </row>
+    <row r="341" spans="1:10">
+      <c r="A341" s="28">
+        <v>2027</v>
+      </c>
+      <c r="B341" s="28">
+        <v>1654</v>
+      </c>
+      <c r="C341" s="28">
+        <v>8</v>
+      </c>
+      <c r="D341" s="28">
+        <v>2</v>
+      </c>
+      <c r="E341" s="29">
+        <v>46284</v>
+      </c>
+      <c r="F341" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G341" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="I341" s="13"/>
+      <c r="J341" s="14"/>
+    </row>
+    <row r="342" spans="1:10">
+      <c r="A342" s="28">
+        <v>2027</v>
+      </c>
+      <c r="B342" s="28">
+        <v>1654</v>
+      </c>
+      <c r="C342" s="28">
+        <v>8</v>
+      </c>
+      <c r="D342" s="28">
+        <v>3</v>
+      </c>
+      <c r="E342" s="29">
+        <v>46284</v>
+      </c>
+      <c r="F342" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="G342" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I342" s="13"/>
+      <c r="J342" s="14"/>
+    </row>
+    <row r="343" spans="1:10">
+      <c r="A343" s="28">
+        <v>2027</v>
+      </c>
+      <c r="B343" s="28">
+        <v>1654</v>
+      </c>
+      <c r="C343" s="28">
+        <v>8</v>
+      </c>
+      <c r="D343" s="28">
+        <v>4</v>
+      </c>
+      <c r="E343" s="29">
+        <v>46284</v>
+      </c>
+      <c r="F343" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="G343" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="I343" s="13"/>
+      <c r="J343" s="14"/>
+    </row>
+    <row r="344" spans="1:10">
+      <c r="A344" s="28">
+        <v>2027</v>
+      </c>
+      <c r="B344" s="28">
+        <v>1654</v>
+      </c>
+      <c r="C344" s="28">
+        <v>8</v>
+      </c>
+      <c r="D344" s="28">
+        <v>5</v>
+      </c>
+      <c r="E344" s="29">
+        <v>46284</v>
+      </c>
+      <c r="F344" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G344" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="I344" s="13"/>
+      <c r="J344" s="14"/>
+    </row>
+    <row r="345" spans="1:10">
+      <c r="A345" s="28">
+        <v>2027</v>
+      </c>
+      <c r="B345" s="28">
+        <v>1654</v>
+      </c>
+      <c r="C345" s="28">
+        <v>8</v>
+      </c>
+      <c r="D345" s="28">
+        <v>6</v>
+      </c>
+      <c r="E345" s="29">
+        <v>46284</v>
+      </c>
+      <c r="F345" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G345" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="I345" s="13"/>
+      <c r="J345" s="14"/>
+    </row>
+    <row r="346" spans="1:10">
+      <c r="A346" s="28">
+        <v>2027</v>
+      </c>
+      <c r="B346" s="28">
+        <v>1654</v>
+      </c>
+      <c r="C346" s="28">
+        <v>8</v>
+      </c>
+      <c r="D346" s="28">
+        <v>7</v>
+      </c>
+      <c r="E346" s="29">
+        <v>46284</v>
+      </c>
+      <c r="F346" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="G346" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="I346" s="13"/>
+      <c r="J346" s="14"/>
+    </row>
+    <row r="347" spans="1:10">
+      <c r="A347" s="28">
+        <v>2027</v>
+      </c>
+      <c r="B347" s="28">
+        <v>1654</v>
+      </c>
+      <c r="C347" s="28">
+        <v>8</v>
+      </c>
+      <c r="D347" s="28">
+        <v>8</v>
+      </c>
+      <c r="E347" s="29">
+        <v>46285</v>
+      </c>
+      <c r="F347" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G347" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="I347" s="13"/>
+      <c r="J347" s="14"/>
+    </row>
+    <row r="348" spans="1:10">
+      <c r="A348" s="28">
+        <v>2027</v>
+      </c>
+      <c r="B348" s="28">
+        <v>1654</v>
+      </c>
+      <c r="C348" s="28">
+        <v>8</v>
+      </c>
+      <c r="D348" s="28">
+        <v>9</v>
+      </c>
+      <c r="E348" s="29">
+        <v>46285</v>
+      </c>
+      <c r="F348" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="G348" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="I348" s="13"/>
+      <c r="J348" s="14"/>
+    </row>
+    <row r="349" spans="1:10">
+      <c r="A349" s="28">
+        <v>2027</v>
+      </c>
+      <c r="B349" s="28">
+        <v>1654</v>
+      </c>
+      <c r="C349" s="28">
+        <v>8</v>
+      </c>
+      <c r="D349" s="28">
+        <v>10</v>
+      </c>
+      <c r="E349" s="29">
+        <v>46284</v>
+      </c>
+      <c r="F349" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="G349" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="I349" s="13"/>
+      <c r="J349" s="14"/>
+    </row>
+    <row r="350" spans="1:10">
+      <c r="A350" s="28">
+        <v>2027</v>
+      </c>
+      <c r="B350" s="28">
+        <v>1654</v>
+      </c>
+      <c r="C350" s="28">
+        <v>8</v>
+      </c>
+      <c r="D350" s="28">
+        <v>11</v>
+      </c>
+      <c r="E350" s="29">
+        <v>46284</v>
+      </c>
+      <c r="F350" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G350" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="I350" s="13"/>
+      <c r="J350" s="14"/>
+    </row>
+    <row r="351" spans="1:10">
+      <c r="A351" s="28">
+        <v>2027</v>
+      </c>
+      <c r="B351" s="28">
+        <v>1654</v>
+      </c>
+      <c r="C351" s="28">
+        <v>8</v>
+      </c>
+      <c r="D351" s="28">
+        <v>12</v>
+      </c>
+      <c r="E351" s="29">
+        <v>46284</v>
+      </c>
+      <c r="F351" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="G351" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="I351" s="13"/>
+      <c r="J351" s="14"/>
+    </row>
+    <row r="352" spans="1:10">
+      <c r="A352" s="28">
+        <v>2027</v>
+      </c>
+      <c r="B352" s="28">
+        <v>1654</v>
+      </c>
+      <c r="C352" s="28">
+        <v>8</v>
+      </c>
+      <c r="D352" s="28">
+        <v>13</v>
+      </c>
+      <c r="E352" s="29">
+        <v>46284</v>
+      </c>
+      <c r="F352" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="G352" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="I352" s="13"/>
+      <c r="J352" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
